--- a/suivi .xlsx
+++ b/suivi .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\application_chantier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B2E5CB-D023-4BC4-8EAB-747B8603B0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A582B091-F56B-4930-AB2E-A7D874CB1AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2512,8 +2512,7 @@
   <autoFilter ref="A1:H2720" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="DÉCAPAGE"/>
-        <filter val="DEGAGEMENT D'EMPRISE"/>
+        <filter val="REMBLAIS DE FOUILLE"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2855,7 +2854,7 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="53" customWidth="1"/>
+    <col min="4" max="4" width="30.85546875" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
@@ -2888,7 +2887,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2914,7 +2913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2940,7 +2939,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2966,7 +2965,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2992,7 +2991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -3018,7 +3017,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -3044,7 +3043,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -3070,7 +3069,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -3096,7 +3095,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -3122,7 +3121,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -3148,7 +3147,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -3174,7 +3173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -3200,7 +3199,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -3226,7 +3225,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -3252,7 +3251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -3278,7 +3277,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -3304,7 +3303,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -3330,7 +3329,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -3356,7 +3355,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -3382,7 +3381,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -3408,7 +3407,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -3434,7 +3433,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -3460,7 +3459,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -3486,7 +3485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -3512,7 +3511,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -3668,7 +3667,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>84</v>
       </c>
@@ -3694,7 +3693,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -4370,7 +4369,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>107</v>
       </c>
@@ -4422,7 +4421,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>107</v>
       </c>
@@ -4448,7 +4447,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>107</v>
       </c>
@@ -5072,7 +5071,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>127</v>
       </c>
@@ -5098,7 +5097,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>127</v>
       </c>
@@ -6591,7 +6590,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>147</v>
       </c>
@@ -9607,7 +9606,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>186</v>
       </c>
@@ -14229,7 +14228,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>251</v>
       </c>
@@ -18227,7 +18226,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>294</v>
       </c>
@@ -18331,7 +18330,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>294</v>
       </c>
@@ -18357,7 +18356,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>294</v>
       </c>
@@ -18539,7 +18538,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>297</v>
       </c>
@@ -18565,7 +18564,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>297</v>
       </c>
@@ -18591,7 +18590,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>297</v>
       </c>
@@ -18617,7 +18616,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>297</v>
       </c>
@@ -18773,7 +18772,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>301</v>
       </c>
@@ -18799,7 +18798,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>301</v>
       </c>
@@ -18877,7 +18876,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>303</v>
       </c>
@@ -19163,7 +19162,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>306</v>
       </c>
@@ -19189,7 +19188,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>306</v>
       </c>
@@ -19475,7 +19474,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>312</v>
       </c>
@@ -19761,7 +19760,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="652" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>315</v>
       </c>
@@ -19787,7 +19786,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>315</v>
       </c>
@@ -19813,7 +19812,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="654" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>315</v>
       </c>
@@ -20073,7 +20072,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>323</v>
       </c>
@@ -20099,7 +20098,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>323</v>
       </c>
@@ -20125,7 +20124,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="666" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>323</v>
       </c>
@@ -20229,7 +20228,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>323</v>
       </c>
@@ -20330,7 +20329,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>327</v>
       </c>
@@ -20720,7 +20719,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="689" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>335</v>
       </c>
@@ -20824,7 +20823,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="693" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>335</v>
       </c>
@@ -20925,7 +20924,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="697" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>335</v>
       </c>
@@ -20951,7 +20950,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="698" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>335</v>
       </c>
@@ -20974,7 +20973,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="699" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>335</v>
       </c>
@@ -21153,7 +21152,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="706" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>343</v>
       </c>
@@ -21179,7 +21178,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="707" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>343</v>
       </c>
@@ -21465,7 +21464,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="718" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>348</v>
       </c>
@@ -21491,7 +21490,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="719" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>348</v>
       </c>
@@ -21517,7 +21516,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="720" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>348</v>
       </c>
@@ -22271,7 +22270,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="749" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>355</v>
       </c>
@@ -22297,7 +22296,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="750" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>355</v>
       </c>
@@ -22375,7 +22374,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="753" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>355</v>
       </c>
@@ -22401,7 +22400,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="754" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>355</v>
       </c>
@@ -22921,7 +22920,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="774" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>357</v>
       </c>
@@ -22947,7 +22946,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="775" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>357</v>
       </c>
@@ -23207,7 +23206,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="785" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>357</v>
       </c>
@@ -23233,7 +23232,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="786" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>357</v>
       </c>
@@ -23259,7 +23258,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="787" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>357</v>
       </c>
@@ -24429,7 +24428,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="832" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>364</v>
       </c>
@@ -24637,7 +24636,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="840" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>365</v>
       </c>
@@ -24663,7 +24662,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="841" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>365</v>
       </c>
@@ -24767,7 +24766,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="845" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>365</v>
       </c>
@@ -27731,7 +27730,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="959" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>384</v>
       </c>
@@ -28329,7 +28328,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="982" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>385</v>
       </c>
@@ -28589,7 +28588,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="992" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>385</v>
       </c>
@@ -28823,7 +28822,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="1001" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>385</v>
       </c>
@@ -37683,7 +37682,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="1342" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1342" t="s">
         <v>469</v>
       </c>
@@ -37709,7 +37708,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1343" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1343" t="s">
         <v>469</v>
       </c>
@@ -37735,7 +37734,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1344" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1344" t="s">
         <v>469</v>
       </c>
@@ -38099,7 +38098,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="1358" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1358" t="s">
         <v>470</v>
       </c>
@@ -38125,7 +38124,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1359" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1359" t="s">
         <v>470</v>
       </c>
@@ -38151,7 +38150,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1360" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1360" t="s">
         <v>470</v>
       </c>
@@ -38177,7 +38176,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1361" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1361" t="s">
         <v>470</v>
       </c>
@@ -38203,7 +38202,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1362" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1362" t="s">
         <v>470</v>
       </c>
@@ -41193,7 +41192,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="1477" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1477" t="s">
         <v>486</v>
       </c>
@@ -41219,7 +41218,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1478" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1478" t="s">
         <v>486</v>
       </c>
@@ -41245,7 +41244,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1479" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1479" t="s">
         <v>486</v>
       </c>
@@ -41271,7 +41270,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1480" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1480" t="s">
         <v>486</v>
       </c>
@@ -41323,7 +41322,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1482" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1482" t="s">
         <v>492</v>
       </c>
@@ -41349,7 +41348,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1483" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1483" t="s">
         <v>492</v>
       </c>
@@ -41375,7 +41374,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1484" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1484" t="s">
         <v>492</v>
       </c>
@@ -41401,7 +41400,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1485" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1485" t="s">
         <v>492</v>
       </c>
@@ -41427,7 +41426,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1486" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1486" t="s">
         <v>492</v>
       </c>
@@ -41713,7 +41712,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="1497" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1497" t="s">
         <v>492</v>
       </c>
@@ -41817,7 +41816,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="1501" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1501" t="s">
         <v>492</v>
       </c>
@@ -41843,7 +41842,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1502" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1502" t="s">
         <v>492</v>
       </c>
@@ -41869,7 +41868,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1503" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1503" t="s">
         <v>492</v>
       </c>
@@ -41895,7 +41894,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1504" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1504" t="s">
         <v>492</v>
       </c>
@@ -41947,7 +41946,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="1506" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1506" t="s">
         <v>495</v>
       </c>
@@ -41973,7 +41972,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1507" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1507" t="s">
         <v>495</v>
       </c>
@@ -41999,7 +41998,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1508" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1508" t="s">
         <v>495</v>
       </c>
@@ -42025,7 +42024,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1509" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1509" t="s">
         <v>495</v>
       </c>
@@ -42051,7 +42050,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1510" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1510" t="s">
         <v>495</v>
       </c>
@@ -42077,7 +42076,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1511" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1511" t="s">
         <v>495</v>
       </c>
@@ -42455,7 +42454,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="1526" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1526" t="s">
         <v>495</v>
       </c>
@@ -42481,7 +42480,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1527" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1527" t="s">
         <v>495</v>
       </c>
@@ -42533,7 +42532,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1529" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1529" t="s">
         <v>495</v>
       </c>
@@ -42559,7 +42558,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1530" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1530" t="s">
         <v>495</v>
       </c>
@@ -42585,7 +42584,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1531" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1531" t="s">
         <v>495</v>
       </c>
@@ -42611,7 +42610,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1532" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1532" t="s">
         <v>495</v>
       </c>
@@ -43105,7 +43104,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1551" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1551" t="s">
         <v>496</v>
       </c>
@@ -43131,7 +43130,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1552" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1552" t="s">
         <v>496</v>
       </c>
@@ -43157,7 +43156,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1553" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1553" t="s">
         <v>496</v>
       </c>
@@ -43885,7 +43884,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1581" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1581" t="s">
         <v>498</v>
       </c>
@@ -48539,7 +48538,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1760" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1760" t="s">
         <v>539</v>
       </c>
@@ -48591,7 +48590,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1762" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1762" t="s">
         <v>539</v>
       </c>
@@ -49501,7 +49500,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="1797" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1797" t="s">
         <v>543</v>
       </c>
@@ -49813,7 +49812,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1809" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1809" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1809" t="s">
         <v>545</v>
       </c>
@@ -49839,7 +49838,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1810" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1810" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1810" t="s">
         <v>545</v>
       </c>
@@ -49865,7 +49864,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1811" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1811" t="s">
         <v>545</v>
       </c>
@@ -50177,7 +50176,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1823" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1823" t="s">
         <v>547</v>
       </c>
@@ -50411,7 +50410,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="1832" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1832" t="s">
         <v>551</v>
       </c>
@@ -50697,7 +50696,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1843" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1843" t="s">
         <v>555</v>
       </c>
@@ -50827,7 +50826,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1848" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1848" t="s">
         <v>556</v>
       </c>
@@ -50853,7 +50852,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1849" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1849" t="s">
         <v>556</v>
       </c>
@@ -51061,7 +51060,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1857" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1857" t="s">
         <v>557</v>
       </c>
@@ -51191,7 +51190,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1862" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1862" t="s">
         <v>558</v>
       </c>
@@ -51217,7 +51216,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1863" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1863" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1863" t="s">
         <v>558</v>
       </c>
@@ -51243,7 +51242,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1864" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1864" t="s">
         <v>558</v>
       </c>
@@ -51503,7 +51502,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1874" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1874" t="s">
         <v>559</v>
       </c>
@@ -51529,7 +51528,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1875" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1875" t="s">
         <v>559</v>
       </c>
@@ -51607,7 +51606,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1878" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1878" t="s">
         <v>560</v>
       </c>
@@ -51659,7 +51658,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1880" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1880" t="s">
         <v>560</v>
       </c>
@@ -51867,7 +51866,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1888" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1888" t="s">
         <v>563</v>
       </c>
@@ -51919,7 +51918,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1890" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1890" t="s">
         <v>563</v>
       </c>
@@ -52049,7 +52048,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1895" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1895" t="s">
         <v>564</v>
       </c>
@@ -52283,7 +52282,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1904" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1904" t="s">
         <v>565</v>
       </c>
@@ -52309,7 +52308,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1905" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1905" t="s">
         <v>565</v>
       </c>
@@ -52517,7 +52516,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="1913" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1913" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1913" t="s">
         <v>566</v>
       </c>
@@ -53357,7 +53356,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1946" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1946" t="s">
         <v>576</v>
       </c>
@@ -53637,7 +53636,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1957" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1957" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1957" t="s">
         <v>580</v>
       </c>
@@ -53663,7 +53662,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="1958" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1958" t="s">
         <v>580</v>
       </c>
@@ -54099,7 +54098,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1975" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1975" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1975" t="s">
         <v>581</v>
       </c>
@@ -54353,7 +54352,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="1985" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1985" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1985" t="s">
         <v>582</v>
       </c>
@@ -54893,7 +54892,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2006" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2006" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2006" t="s">
         <v>583</v>
       </c>
@@ -54919,7 +54918,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2007" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2007" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2007" t="s">
         <v>583</v>
       </c>
@@ -54971,7 +54970,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2009" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2009" t="s">
         <v>589</v>
       </c>
@@ -55251,7 +55250,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2020" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2020" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2020" t="s">
         <v>589</v>
       </c>
@@ -55277,7 +55276,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2021" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2021" t="s">
         <v>589</v>
       </c>
@@ -55609,7 +55608,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2034" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2034" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2034" t="s">
         <v>593</v>
       </c>
@@ -55635,7 +55634,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2035" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2035" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2035" t="s">
         <v>593</v>
       </c>
@@ -56045,7 +56044,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2051" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2051" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2051" t="s">
         <v>596</v>
       </c>
@@ -56071,7 +56070,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2052" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2052" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2052" t="s">
         <v>596</v>
       </c>
@@ -56149,7 +56148,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2055" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2055" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2055" t="s">
         <v>598</v>
       </c>
@@ -56377,7 +56376,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2064" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2064" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2064" t="s">
         <v>598</v>
       </c>
@@ -56403,7 +56402,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2065" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2065" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2065" t="s">
         <v>598</v>
       </c>
@@ -56891,7 +56890,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2084" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2084" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2084" t="s">
         <v>602</v>
       </c>
@@ -56917,7 +56916,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2085" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2085" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2085" t="s">
         <v>602</v>
       </c>
@@ -57119,7 +57118,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2093" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2093" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2093" t="s">
         <v>603</v>
       </c>
@@ -57145,7 +57144,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2094" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2094" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2094" t="s">
         <v>603</v>
       </c>
@@ -57341,7 +57340,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2102" t="s">
         <v>604</v>
       </c>
@@ -57575,7 +57574,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2111" t="s">
         <v>606</v>
       </c>
@@ -57601,7 +57600,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2112" t="s">
         <v>606</v>
       </c>
@@ -57627,7 +57626,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2113" t="s">
         <v>606</v>
       </c>
@@ -57835,7 +57834,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2121" t="s">
         <v>608</v>
       </c>
@@ -57861,7 +57860,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2122" t="s">
         <v>608</v>
       </c>
@@ -57887,7 +57886,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2123" t="s">
         <v>608</v>
       </c>
@@ -58225,7 +58224,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2136" t="s">
         <v>611</v>
       </c>
@@ -58459,7 +58458,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2145" t="s">
         <v>613</v>
       </c>
@@ -58537,7 +58536,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="2148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2148" t="s">
         <v>615</v>
       </c>
@@ -58563,7 +58562,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2149" t="s">
         <v>615</v>
       </c>
@@ -58667,7 +58666,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2153" t="s">
         <v>617</v>
       </c>
@@ -58693,7 +58692,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2154" t="s">
         <v>617</v>
       </c>
@@ -58875,7 +58874,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2161" t="s">
         <v>617</v>
       </c>
@@ -58901,7 +58900,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2162" t="s">
         <v>618</v>
       </c>
@@ -58927,7 +58926,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2163" t="s">
         <v>618</v>
       </c>
@@ -58953,7 +58952,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2164" t="s">
         <v>619</v>
       </c>
@@ -58979,7 +58978,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2165" t="s">
         <v>619</v>
       </c>
@@ -59213,7 +59212,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2174" t="s">
         <v>623</v>
       </c>
@@ -59239,7 +59238,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2175" t="s">
         <v>623</v>
       </c>
@@ -61293,7 +61292,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="2254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2254" t="s">
         <v>650</v>
       </c>
@@ -61527,7 +61526,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2263" t="s">
         <v>652</v>
       </c>
@@ -61553,7 +61552,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2264" t="s">
         <v>652</v>
       </c>
@@ -61891,7 +61890,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2277" t="s">
         <v>653</v>
       </c>
@@ -61917,7 +61916,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2278" t="s">
         <v>653</v>
       </c>
@@ -62463,7 +62462,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2299" t="s">
         <v>654</v>
       </c>
@@ -62489,7 +62488,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2300" t="s">
         <v>654</v>
       </c>
@@ -62697,7 +62696,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2308" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2308" t="s">
         <v>655</v>
       </c>
@@ -62723,7 +62722,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2309" t="s">
         <v>655</v>
       </c>
@@ -62879,7 +62878,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2315" t="s">
         <v>656</v>
       </c>
@@ -62905,7 +62904,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2316" t="s">
         <v>656</v>
       </c>
@@ -63165,7 +63164,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2326" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2326" t="s">
         <v>661</v>
       </c>
@@ -69428,7 +69427,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2567" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2567" t="s">
         <v>712</v>
       </c>
@@ -69454,7 +69453,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2568" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2568" t="s">
         <v>712</v>
       </c>
@@ -69480,7 +69479,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2569" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2569" t="s">
         <v>713</v>
       </c>
@@ -69506,7 +69505,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2570" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2570" t="s">
         <v>713</v>
       </c>
@@ -69532,7 +69531,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2571" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2571" t="s">
         <v>713</v>
       </c>
@@ -69558,7 +69557,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2572" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2572" t="s">
         <v>714</v>
       </c>
@@ -69584,7 +69583,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2573" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2573" t="s">
         <v>714</v>
       </c>
@@ -69610,7 +69609,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2574" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2574" t="s">
         <v>715</v>
       </c>
@@ -69636,7 +69635,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2575" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2575" t="s">
         <v>715</v>
       </c>
@@ -70468,7 +70467,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="2607" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2607" t="s">
         <v>738</v>
       </c>
@@ -70546,7 +70545,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="2610" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2610" t="s">
         <v>740</v>
       </c>
@@ -70572,7 +70571,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2611" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2611" t="s">
         <v>740</v>
       </c>
@@ -70624,7 +70623,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="2613" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2613" t="s">
         <v>741</v>
       </c>
@@ -70650,7 +70649,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2614" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2614" t="s">
         <v>741</v>
       </c>
@@ -70728,7 +70727,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="2617" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2617" t="s">
         <v>742</v>
       </c>
@@ -70754,7 +70753,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2618" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2618" t="s">
         <v>742</v>
       </c>
@@ -70806,7 +70805,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="2620" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2620" t="s">
         <v>743</v>
       </c>
@@ -70832,7 +70831,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2621" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2621" t="s">
         <v>743</v>
       </c>
